--- a/Result/profitability/6662.xlsx
+++ b/Result/profitability/6662.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM39"/>
+  <dimension ref="A1:AM40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5383,6 +5383,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>6662</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>65</v>
+      </c>
+      <c r="D40" t="n">
+        <v>39</v>
+      </c>
+      <c r="E40" t="n">
+        <v>26</v>
+      </c>
+      <c r="F40" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="G40" t="n">
+        <v>11</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>17.58%</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>13</v>
+      </c>
+      <c r="K40" t="n">
+        <v>10</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.43625</v>
+      </c>
+      <c r="N40" t="n">
+        <v>40.13625</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.109999999999999</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.2151937046004841</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-0.09000000000000002</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>-2.920000000000002</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>-0.06779661016949157</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK40" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
